--- a/Template Import/AP Template Rate.xlsx
+++ b/Template Import/AP Template Rate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MSIG\pregolive\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MSIGSX\MSIGSX\Template Import\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F982C3E-D1CF-432C-BBE2-0C0E255486EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7F9A415-8135-4573-85A3-ACCF4C174A28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24" yWindow="24" windowWidth="23016" windowHeight="13656" xr2:uid="{3C3CB582-22BF-429F-A34F-2F202773D1D2}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{3C3CB582-22BF-429F-A34F-2F202773D1D2}"/>
   </bookViews>
   <sheets>
     <sheet name="AP Template Rate H" sheetId="1" r:id="rId1"/>
@@ -203,24 +203,6 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{2A606A95-610C-4164-AAD7-E1FA7CC20C12}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Description: Object Type_x000D_
-Type: string_x000D_
-Field Length: 20_x000D_
-Related Table: ADP1_x000D_
-</t>
-        </r>
-      </text>
-    </comment>
     <comment ref="A2" authorId="0" shapeId="0" xr:uid="{144DA908-EA7F-421D-B7FD-04A1E9262153}">
       <text>
         <r>
@@ -400,7 +382,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="38">
   <si>
     <t>DocNum</t>
   </si>
@@ -511,12 +493,6 @@
   </si>
   <si>
     <t>Comments</t>
-  </si>
-  <si>
-    <t>DocObjectCode</t>
-  </si>
-  <si>
-    <t>ObjType</t>
   </si>
   <si>
     <t>PolicyNO</t>
@@ -1013,7 +989,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED8573E7-2B3E-48AA-91C0-6A7353CFE377}">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="18.600000000000001" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="12.59765625" style="6" bestFit="1" customWidth="1"/>
@@ -1024,14 +1000,13 @@
     <col min="6" max="7" width="13.59765625" style="6" customWidth="1"/>
     <col min="8" max="8" width="19" style="6" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="36.3984375" style="6" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="36.3984375" style="6" customWidth="1"/>
-    <col min="11" max="11" width="12.69921875" style="6" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="27.09765625" style="6" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="24.796875" style="6" customWidth="1"/>
-    <col min="14" max="16384" width="8.796875" style="6"/>
+    <col min="10" max="10" width="12.69921875" style="6" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="27.09765625" style="6" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="24.796875" style="6" customWidth="1"/>
+    <col min="13" max="16384" width="8.796875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1059,20 +1034,17 @@
       <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
-        <v>37</v>
+      <c r="J1" s="5" t="s">
+        <v>36</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="M1" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A2" s="7" t="s">
         <v>0</v>
       </c>
@@ -1100,20 +1072,17 @@
       <c r="I2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="9" t="s">
-        <v>38</v>
+      <c r="J2" s="5" t="s">
+        <v>37</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="M2" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A3" s="6">
         <v>1</v>
       </c>
@@ -1139,15 +1108,12 @@
         <v>111</v>
       </c>
       <c r="J3" s="6">
-        <v>18</v>
-      </c>
-      <c r="K3" s="6">
         <v>56</v>
       </c>
+      <c r="K3" s="6" t="s">
+        <v>15</v>
+      </c>
       <c r="L3" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="M3" s="6" t="s">
         <v>16</v>
       </c>
     </row>
